--- a/Horario.xlsx
+++ b/Horario.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unach\Semestre4\EstudioGITClaude\UNACH-4toSemestre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A2698F95-D587-43CE-AD24-ECD537EBB326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E19CA93-DB14-4D9A-A63C-37D6AD2AA471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{4E1D122C-2A65-485C-9CCF-751C2E3B092D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4E1D122C-2A65-485C-9CCF-751C2E3B092D}"/>
   </bookViews>
   <sheets>
     <sheet name="HORARIO" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="20">
   <si>
     <t>Machine Learning 1 - Sesión de transmisión en vivo - Día lunes 18:00 a 20:00: ➢https://cedia.zoom.us/j/85982729258</t>
   </si>
@@ -92,6 +92,12 @@
   </si>
   <si>
     <t>Jueves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viernes </t>
+  </si>
+  <si>
+    <t>Ingles</t>
   </si>
 </sst>
 </file>
@@ -214,16 +220,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>624840</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>54046</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>38436</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>983686</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>7956</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -246,57 +252,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="624840" y="182880"/>
+          <a:off x="5364480" y="1348740"/>
           <a:ext cx="8146486" cy="3878916"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>332360</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>41063</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>175260</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagen 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0048DC2-529D-481E-B3CF-9CE786B07EB8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7518020" y="2293620"/>
-          <a:ext cx="5873283" cy="2796540"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -605,11 +562,126 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A43AED0E-8E59-4B3F-9A7C-3437235D4C0E}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="18.88671875" defaultRowHeight="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="27" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="https://cedia.zoom.us/j/85982729258" xr:uid="{E538D54A-1663-44BC-80BF-7B23662ACAD4}"/>
+    <hyperlink ref="B3" r:id="rId2" display="https://cedia.zoom.us/j/85982729258" xr:uid="{63BC7D96-23F4-435A-8173-B9D57ECF50CE}"/>
+    <hyperlink ref="B4" r:id="rId3" display="https://cedia.zoom.us/j/87038781387" xr:uid="{311A8F0A-8DCE-49DD-A7B7-A031AC86C8A1}"/>
+    <hyperlink ref="B5" r:id="rId4" display="https://cedia.zoom.us/j/87038781387" xr:uid="{C3C12CC1-49FE-4A07-853C-2BC787D6EAB2}"/>
+    <hyperlink ref="C2" r:id="rId5" display="https://cedia.zoom.us/j/81389632654" xr:uid="{4691880A-FB84-431B-A606-01C38A13F8F8}"/>
+    <hyperlink ref="C3" r:id="rId6" display="https://cedia.zoom.us/j/81389632654" xr:uid="{0994F787-E7A3-4D01-9850-1D752E144167}"/>
+    <hyperlink ref="C4" r:id="rId7" display="https://cedia.zoom.us/j/87349957464" xr:uid="{8C019164-AF71-47D8-9AF9-06AB980B4761}"/>
+    <hyperlink ref="C5" r:id="rId8" display="https://cedia.zoom.us/j/87349957464" xr:uid="{6DD4C4B6-3B98-4849-9354-020783AA9DB9}"/>
+    <hyperlink ref="D3" r:id="rId9" display="https://cedia.zoom.us/j/85982729258" xr:uid="{A9E2890D-D4D7-4A39-8578-007E5BCAD39D}"/>
+    <hyperlink ref="D4" r:id="rId10" display="https://cedia.zoom.us/j/82520483561" xr:uid="{361C5D15-DFAC-40F0-83A2-34024D6EA0B6}"/>
+    <hyperlink ref="D5" r:id="rId11" display="https://cedia.zoom.us/j/82520483561" xr:uid="{9C320C08-35A4-449C-9A13-918516B4AA94}"/>
+    <hyperlink ref="E2" r:id="rId12" display="https://cedia.zoom.us/j/82520483561" xr:uid="{039455D4-113F-4118-9E41-B9E750E4ADF1}"/>
+    <hyperlink ref="E3" r:id="rId13" display="https://cedia.zoom.us/j/81389632654" xr:uid="{B2C42C9D-821B-43D6-AA9F-B1341B704CA8}"/>
+    <hyperlink ref="E4" r:id="rId14" display="https://cedia.zoom.us/j/87038781387" xr:uid="{4EE29304-00F1-4053-931C-45A477865F01}"/>
+    <hyperlink ref="E5" r:id="rId15" display="https://cedia.zoom.us/j/87349957464" xr:uid="{AD5435B2-9459-448D-8288-18EF0A7A7C0D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId16"/>
 </worksheet>
 </file>
 
@@ -775,6 +847,5 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId26"/>
-  <drawing r:id="rId27"/>
 </worksheet>
 </file>